--- a/ig/document/StructureDefinition-medcom-document-composition.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2517,7 +2517,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>166</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>173</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>183</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>191</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>213</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>243</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>251</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>272</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>284</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>297</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>306</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>319</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>324</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>345</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>356</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>359</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>361</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>362</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>365</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>385</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>408</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>412</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>419</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>427</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>443</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>457</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>499</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>510</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>517</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>523</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>530</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>537</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>542</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>596</v>
       </c>
@@ -14235,12 +14235,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO102">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-composition.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
